--- a/data/mapping/phase1_hop3_il_to_consumption.xlsx
+++ b/data/mapping/phase1_hop3_il_to_consumption.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -501,6 +501,48 @@
       <c r="A12" t="inlineStr">
         <is>
           <t xml:space="preserve">  - PARTY_TAX_IDENTIFIER_FORMAT_INDICATOR: LEFT(x,1) -&gt; substr(x,0,1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - CUSTOMER_CATEGORY: client CASE — DIM_REFERENCE match on</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ATTRIBUTE_MAP_CD = NAICS_CD returns ATTRIBUTE_CD; else 'P' -&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INDIVIDUAL, 'C'/'B' + name LIKE %LLC%/%INC% -&gt; CORP_SMALL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    'C'/'B' + name LIKE %BANK% -&gt; BANK, otherwise NULL (spec has</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    no ELSE — declared ELSE NULL). V_PARTY_SNPSHT_SRC LEFT JOINs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    DIM_REFERENCE to expose attribute_cd.</t>
         </is>
       </c>
     </row>
@@ -625,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1391,6 +1433,54 @@
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cl_party_snpsht_migration</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>attribute_cd</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>customer_category</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>case(notnull(attribute_cd), attribute_cd, case(eq(customer_type_cd, 'P'), 'INDIVIDUAL', booland(in_list(customer_type_cd, 'C', 'B'), boolor(like(upper(full_nm), '%LLC%'), like(upper(full_nm), '%INC%'))), 'CORP_SMALL', booland(in_list(customer_type_cd, 'C', 'B'), like(upper(full_nm), '%BANK%')), 'BANK', None))</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>yes</t>
         </is>

--- a/data/mapping/phase1_hop3_il_to_consumption.xlsx
+++ b/data/mapping/phase1_hop3_il_to_consumption.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,6 +611,11 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -653,6 +658,11 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>REQ-DA-301</t>
         </is>
       </c>
     </row>
@@ -667,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +731,16 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Business Rule</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -765,6 +785,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -805,6 +831,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -853,6 +885,16 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>decode customer type: 'P'-&gt;Personal, 'N'-&gt;Non-Personal, 'C'-&gt;Commercial, 'B'-&gt;Business, otherwise UNSPECIFIED</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>REQ-DA-303</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -899,6 +941,16 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>keep the country code only if it is two letters, otherwise 'US' — padded numeric codes never match, so 'US' always wins (per spec)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>REQ-DA-304</t>
         </is>
       </c>
     </row>
@@ -945,6 +997,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -989,6 +1047,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1033,6 +1097,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1081,6 +1151,16 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>'PAR' maps to 'BROKER-DEALER'; otherwise the NAICS code</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>REQ-DA-305</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1127,6 +1207,16 @@
       <c r="J10" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>spec gap sentinel — party type rule pending client spec</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>REQ-DA-306</t>
         </is>
       </c>
     </row>
@@ -1173,6 +1263,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1217,6 +1313,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1261,6 +1363,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1305,6 +1413,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1351,6 +1465,16 @@
       <c r="J15" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>first character of the tax-id type code</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>REQ-DA-307</t>
         </is>
       </c>
     </row>
@@ -1393,6 +1517,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1437,6 +1567,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1483,6 +1619,16 @@
       <c r="J18" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NAICS-match in DIM_REFERENCE wins; else 'P'-&gt;INDIVIDUAL, 'C'/'B' + LLC/INC in name-&gt;CORP_SMALL, +BANK-&gt;BANK, else NULL</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>REQ-DA-308</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1536,6 +1682,11 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1565,6 +1716,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>REQ-DC-301</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1596,6 +1752,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>REQ-DA-302</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1637,6 +1798,11 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Enabled</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
         </is>
       </c>
     </row>

--- a/data/mapping/phase1_hop3_il_to_consumption.xlsx
+++ b/data/mapping/phase1_hop3_il_to_consumption.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,6 +611,11 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Source Tables</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -653,6 +658,11 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>dim_customer, dim_customer_address, dim_reference</t>
         </is>
       </c>
     </row>
@@ -667,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +731,11 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -763,6 +778,11 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Customer key - copied unchanged as the party identifier</t>
         </is>
       </c>
     </row>
@@ -805,6 +825,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Snapshot as-of date</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -853,6 +878,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Type code expanded: P=Personal, N=Non-Personal, C=Commercial, B=Business</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -899,6 +929,11 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Two-letter country code kept; anything else defaults to 'US'</t>
         </is>
       </c>
     </row>
@@ -945,6 +980,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Legal entity code - copied unchanged</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -989,6 +1029,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Bank code - copied unchanged</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1033,6 +1078,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Source system code - copied unchanged</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1081,6 +1131,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>'PAR' becomes 'BROKER-DEALER'; otherwise the NAICS code</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1127,6 +1182,11 @@
       <c r="J10" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SPEC GAP - placeholder until the client defines party type logic</t>
         </is>
       </c>
     </row>
@@ -1173,6 +1233,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full name - copied unchanged (PII)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1217,6 +1282,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>First name - copied unchanged (PII)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1261,6 +1331,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Last name - copied unchanged</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1305,6 +1380,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tax id - copied unchanged (PII)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1351,6 +1431,11 @@
       <c r="J15" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>First character of the tax-id type code</t>
         </is>
       </c>
     </row>
@@ -1393,6 +1478,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Birth date - copied unchanged (PII)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1437,6 +1527,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tax-id type description - copied unchanged</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1483,6 +1578,11 @@
       <c r="J18" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Client CASE: NAICS lookup in dim_reference wins; else name/type markers classify the category; NULL for unmatched C/B names</t>
         </is>
       </c>
     </row>
